--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,16 +452,6 @@
   </si>
   <si>
     <t>Code de la batterie d'examen</t>
-  </si>
-  <si>
-    <t>fr-lm-batterie-examens-biologie-medicale.choice[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-sujet-non-humain
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-sujet-non-humain</t>
-  </si>
-  <si>
-    <t>Sujet non humain ou Patient avec sujet non humain</t>
   </si>
   <si>
     <t>fr-lm-batterie-examens-biologie-medicale.laboratoireExecutant</t>
@@ -813,7 +803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.97265625" customWidth="true" bestFit="true"/>
@@ -2879,7 +2869,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2954,7 +2944,7 @@
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
@@ -3360,106 +3350,6 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-batterie-examens-biologie-medicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
